--- a/results/Int All Data -0.8/Rando_6_permute.xlsx
+++ b/results/Int All Data -0.8/Rando_6_permute.xlsx
@@ -440,1477 +440,1477 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8771104867867604</v>
+        <v>0.9003116744219457</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8769115499118053</v>
+        <v>0.9012666512359228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8862238708287107</v>
+        <v>0.9012666512359228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8783041080364911</v>
+        <v>0.9007093486363744</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8752001340878435</v>
+        <v>0.9035746781492684</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.875000997677407</v>
+        <v>0.9048086055662419</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8810898228923068</v>
+        <v>0.9058831041335771</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8824825805524739</v>
+        <v>0.8985204444054242</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8841937968409543</v>
+        <v>0.8958141446712055</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.871220199375853</v>
+        <v>0.8886510204244519</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8690712022411826</v>
+        <v>0.8868998970396916</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8757173300556305</v>
+        <v>0.8875366147608368</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8728520005427365</v>
+        <v>0.8873376778858817</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8585253529782666</v>
+        <v>0.8696289039116936</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8534314116736238</v>
+        <v>0.8711808908860172</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8591219640676505</v>
+        <v>0.8704647580432753</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8583657245931471</v>
+        <v>0.8701862065112418</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8564956780614729</v>
+        <v>0.8701862065112418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8593610075743668</v>
+        <v>0.8664453153059677</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8619078784589476</v>
+        <v>0.8654107238349122</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8612314531770039</v>
+        <v>0.8614311881938846</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8478996895227909</v>
+        <v>0.8603963971873478</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8431639144072599</v>
+        <v>0.8607545633764596</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8365976007853717</v>
+        <v>0.8633808493826373</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8283994859966</v>
+        <v>0.848457391193302</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8311055861953373</v>
+        <v>0.8457113838982848</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8317423039164824</v>
+        <v>0.8522379899593746</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8295136921247336</v>
+        <v>0.8536307476195417</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8329760317979743</v>
+        <v>0.8469848193405751</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8329760317979743</v>
+        <v>0.8555013927576602</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8329760317979743</v>
+        <v>0.8555013927576602</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8178538362691654</v>
+        <v>0.8525169405623708</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8149487991954729</v>
+        <v>0.8528751067514826</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8149487991954729</v>
+        <v>0.8582475995881588</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8036068033617738</v>
+        <v>0.8528751067514826</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8239033529942295</v>
+        <v>0.8509647540525656</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.822271551827346</v>
+        <v>0.8406575492254034</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8243409343049382</v>
+        <v>0.8451149723443823</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.839463129833747</v>
+        <v>0.8718186062845695</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8356424244359132</v>
+        <v>0.8748830722079</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8381495877596954</v>
+        <v>0.8624681740907167</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8385077539488072</v>
+        <v>0.8618711639303701</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8381495877596954</v>
+        <v>0.8625076821160339</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8377515144743037</v>
+        <v>0.8634229513692124</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8380699731026171</v>
+        <v>0.8485407970245269</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8470241278304108</v>
+        <v>0.8485407970245269</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8463077954521874</v>
+        <v>0.8479437868641801</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8532324747986687</v>
+        <v>0.8454765306366778</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8553417643725407</v>
+        <v>0.8430489819699739</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8612316527124853</v>
+        <v>0.8430489819699739</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8608734865233736</v>
+        <v>0.8545887174657397</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8164602804670726</v>
+        <v>0.8548275614369747</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8088595749096104</v>
+        <v>0.8564990701646567</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7939758242810737</v>
+        <v>0.8417372357152548</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7892799562618225</v>
+        <v>0.8399066972088977</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7883646870086438</v>
+        <v>0.8496563999010305</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7715308761203917</v>
+        <v>0.8610367065471582</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7745157273866439</v>
+        <v>0.8535150170403301</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6729948679474184</v>
+        <v>0.8580512566744618</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6649956900336018</v>
+        <v>0.8533553886552107</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6686170594855176</v>
+        <v>0.8533553886552107</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6608176165885817</v>
+        <v>0.8532759735336137</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6522613356106983</v>
+        <v>0.8532759735336137</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6494756207548826</v>
+        <v>0.8129658155813266</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6492766838799275</v>
+        <v>0.7812895579091874</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6338755377481223</v>
+        <v>0.7801747531746095</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6409594464087603</v>
+        <v>0.7640584718774692</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6409594464087603</v>
+        <v>0.7518411138868714</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6487602860540661</v>
+        <v>0.7593618057162925</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6862083070611615</v>
+        <v>0.7463892059285983</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6651960236569266</v>
+        <v>0.729636805516757</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6675439576665523</v>
+        <v>0.7170620794789729</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6800394681182208</v>
+        <v>0.7562586299095706</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6850551915141551</v>
+        <v>0.7560994005954138</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.683980293875857</v>
+        <v>0.7712597074011701</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6803587248884597</v>
+        <v>0.7711008771579763</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6722003176604864</v>
+        <v>0.7732093685899226</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6313693721017472</v>
+        <v>0.7612715598087652</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6145349626070508</v>
+        <v>0.755660223000854</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6035114254016649</v>
+        <v>0.7591620706994118</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6024766343951281</v>
+        <v>0.7481796378031942</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6024766343951281</v>
+        <v>0.7503280363314204</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5850859199782905</v>
+        <v>0.7560980038470441</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5797531347024127</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5410699890654556</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5394383874340536</v>
+        <v>0.7510030648649944</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5520141111492446</v>
+        <v>0.7516794901469379</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.551019426774469</v>
+        <v>0.7616680368103056</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5561927832007088</v>
+        <v>0.7498503483889505</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5547601184442618</v>
+        <v>0.7540673312528434</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5500243433287307</v>
+        <v>0.7565337893384201</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.547238628472915</v>
+        <v>0.7748381767245851</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5391598359020201</v>
+        <v>0.7260130416390642</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.539716938966087</v>
+        <v>0.7299911805317222</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5354985593538243</v>
+        <v>0.7313043235348109</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5362945063891261</v>
+        <v>0.733214277162765</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5353794366714288</v>
+        <v>0.7149499964083613</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5369711312065512</v>
+        <v>0.7312243098067699</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.532912379979408</v>
+        <v>0.7318610275279149</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5266643254503516</v>
+        <v>0.7342089615375407</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5216494001963429</v>
+        <v>0.679806211140465</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5209330678181194</v>
+        <v>0.684502478230679</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5209330678181194</v>
+        <v>0.6824736014558108</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5253503843053372</v>
+        <v>0.6921027847171783</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.526146331340639</v>
+        <v>0.6680625503827091</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5345838887070898</v>
+        <v>0.6363842973557557</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5403941623899562</v>
+        <v>0.6176006257432697</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5403941623899562</v>
+        <v>0.5958726085672554</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5386033314443974</v>
+        <v>0.5958726085672554</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5304850308481854</v>
+        <v>0.5962307747563671</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5304850308481854</v>
+        <v>0.5781235284258247</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5368134981762457</v>
+        <v>0.5746216807272669</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5324753972751435</v>
+        <v>0.5746216807272669</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5337085265501912</v>
+        <v>0.5812271033035095</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5331115163898444</v>
+        <v>0.5820230503388113</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.532951888004725</v>
+        <v>0.5803904510300021</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5320366187515464</v>
+        <v>0.5803904510300021</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5304844322417412</v>
+        <v>0.5804700656870805</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5304844322417412</v>
+        <v>0.5587013432728608</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5304844322417412</v>
+        <v>0.5193413732829971</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5276197013352915</v>
+        <v>0.5203759647540526</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5267842462746726</v>
+        <v>0.5245149292447183</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5237995945439018</v>
+        <v>0.5247535736804719</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5310024263514538</v>
+        <v>0.5239576266451701</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5317983733867556</v>
+        <v>0.5175106352411586</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5150848823937872</v>
+        <v>0.5175106352411586</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5150852814647501</v>
+        <v>0.5234402311419016</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5098714193357863</v>
+        <v>0.5267433415009857</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5105877517140098</v>
+        <v>0.531957004094468</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.513969878123728</v>
+        <v>0.5351407922356753</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5077607330135445</v>
+        <v>0.5361753837067307</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5045773439433</v>
+        <v>0.5411100956972169</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5038610115650765</v>
+        <v>0.5445329273451405</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5076813178919476</v>
+        <v>0.5443736980309839</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5000409047736869</v>
+        <v>0.5315192232482779</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4989664062063516</v>
+        <v>0.5456471334732742</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5036622742256028</v>
+        <v>0.5505423374384433</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5040597489045502</v>
+        <v>0.5433784150497641</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4997615550997279</v>
+        <v>0.5395182016266132</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5001993359459179</v>
+        <v>0.5283751426678692</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5001993359459179</v>
+        <v>0.541707305393045</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5010744985673352</v>
+        <v>0.5382846732806028</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5010744985673352</v>
+        <v>0.5359367392709772</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5010744985673352</v>
+        <v>0.5120982353082025</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5011541132244136</v>
+        <v>0.5091135835774317</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5010347910065368</v>
+        <v>0.5068851713211643</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5032634027982856</v>
+        <v>0.5044971306797775</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5032634027982856</v>
+        <v>0.5044971306797775</v>
       </c>
     </row>
     <row r="150">
@@ -1920,67 +1920,67 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5027462068304985</v>
+        <v>0.5048157888435721</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5026665921734202</v>
+        <v>0.5024676552984652</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4998806777821232</v>
+        <v>0.5024676552984652</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4996021262500898</v>
+        <v>0.5016320007023649</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4996021262500898</v>
+        <v>0.5032236952374871</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4996021262500898</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4996021262500898</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
